--- a/data/hs_code.xlsx
+++ b/data/hs_code.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21320" windowHeight="7560"/>
+    <workbookView windowWidth="24460" windowHeight="8300"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,12 +27,33 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="31">
+  <si>
+    <t>中文品名</t>
+  </si>
   <si>
     <t>进口海关编码</t>
   </si>
   <si>
-    <t>品名</t>
+    <t>HS CODE</t>
+  </si>
+  <si>
+    <t>英文品名</t>
+  </si>
+  <si>
+    <t>用途</t>
+  </si>
+  <si>
+    <t>材质</t>
+  </si>
+  <si>
+    <t>成分</t>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
+    <t>规格</t>
   </si>
   <si>
     <t>蜡烛</t>
@@ -41,41 +62,97 @@
     <t>CANDLE</t>
   </si>
   <si>
+    <t>用于室内芬香</t>
+  </si>
+  <si>
+    <t>92%植物混合蜡+8%的香精</t>
+  </si>
+  <si>
     <t>挥发液</t>
   </si>
   <si>
     <t>AROMA DIFFUSER</t>
   </si>
   <si>
+    <t>15%的香精  85%的溶剂</t>
+  </si>
+  <si>
     <t>车载香薰</t>
   </si>
   <si>
-    <t>Car DIffuser</t>
+    <t>Car Diffuser</t>
+  </si>
+  <si>
+    <t>用于车内芬香</t>
+  </si>
+  <si>
+    <t>20%的香精 80%的溶剂</t>
   </si>
   <si>
     <t>车载香薰香片</t>
   </si>
   <si>
     <t>Car Aromatherapy Fragrance Tablet</t>
+  </si>
+  <si>
+    <t>10%香精+90%EVA棉</t>
+  </si>
+  <si>
+    <t>150*168mm</t>
+  </si>
+  <si>
+    <t>喷雾</t>
+  </si>
+  <si>
+    <t>6%的香精，10%的增溶剂，84%的水</t>
+  </si>
+  <si>
+    <t>铁夹+10%香精+90%榉木块</t>
+  </si>
+  <si>
+    <t>遮阳板车载</t>
+  </si>
+  <si>
+    <t>128*89.5*48MM</t>
+  </si>
+  <si>
+    <t>液体挂件车载香氛香薰</t>
+  </si>
+  <si>
+    <t>8ML</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="&quot;￥&quot;#,##0_);[Red]\(&quot;￥&quot;#,##0\)"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF171A1D"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -416,12 +493,40 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="11">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -542,142 +647,184 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1204,62 +1351,227 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="4" outlineLevelCol="2"/>
+  <dimension ref="A1:I8"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="7"/>
   <cols>
-    <col min="2" max="2" width="15.1538461538462" style="1" customWidth="1"/>
+    <col min="1" max="3" width="15.1538461538462" style="3" customWidth="1"/>
+    <col min="4" max="4" width="37" style="2" customWidth="1"/>
+    <col min="5" max="5" width="15.1538461538462" style="3" customWidth="1"/>
+    <col min="6" max="7" width="38.8461538461538" customWidth="1"/>
+    <col min="8" max="8" width="24.8461538461538" customWidth="1"/>
+    <col min="9" max="9" width="16.3846153846154" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="B1" s="1" t="s">
+    <row r="1" s="1" customFormat="1" ht="17" spans="1:9">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
+      <c r="C1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="1">
+    <row r="2" s="1" customFormat="1" spans="1:9">
+      <c r="A2" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="4">
         <v>3406000090</v>
       </c>
-      <c r="C2" t="s">
-        <v>3</v>
-      </c>
+      <c r="C2" s="4">
+        <v>3406000090</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
     </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="1">
+    <row r="3" s="1" customFormat="1" spans="1:9">
+      <c r="A3" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="4">
         <v>3307490000</v>
       </c>
-      <c r="C3" t="s">
-        <v>5</v>
-      </c>
+      <c r="C3" s="4">
+        <v>3307490000</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="8"/>
+      <c r="I3" s="8"/>
     </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="1">
+    <row r="4" s="2" customFormat="1" spans="1:9">
+      <c r="A4" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="7">
         <v>3307490000</v>
       </c>
-      <c r="C4" t="s">
-        <v>7</v>
-      </c>
+      <c r="C4" s="7">
+        <v>3307490000</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
     </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="1">
+    <row r="5" s="2" customFormat="1" spans="1:9">
+      <c r="A5" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="7">
         <v>3307490000</v>
       </c>
-      <c r="C5" t="s">
-        <v>9</v>
+      <c r="C5" s="7">
+        <v>3307490000</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G5" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="H5" s="13"/>
+      <c r="I5" s="13" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" s="2" customFormat="1" spans="1:9">
+      <c r="A6" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="7">
+        <v>3307490000</v>
+      </c>
+      <c r="C6" s="7">
+        <v>3307490000</v>
+      </c>
+      <c r="D6" s="13"/>
+      <c r="E6" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="G6" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+    </row>
+    <row r="7" s="2" customFormat="1" spans="1:9">
+      <c r="A7" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="7">
+        <v>3307490000</v>
+      </c>
+      <c r="C7" s="7">
+        <v>3307490000</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="G7" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="H7" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="I7" s="13" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" s="2" customFormat="1" spans="1:9">
+      <c r="A8" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="7">
+        <v>3307490000</v>
+      </c>
+      <c r="C8" s="7">
+        <v>3307490000</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="F8" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="G8" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="H8" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="I8" s="13" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
